--- a/data/trans_dic/LAWTONB_2R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 39,42</t>
+          <t>12,86; 43,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 46,23</t>
+          <t>18,5; 47,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,59; 36,85</t>
+          <t>12,58; 38,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,28; 60,02</t>
+          <t>38,98; 60,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 41,78</t>
+          <t>12,21; 44,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 74,93</t>
+          <t>48,04; 75,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,29; 67,66</t>
+          <t>36,43; 67,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,23; 61,14</t>
+          <t>44,03; 61,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 36,86</t>
+          <t>16,51; 36,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,92; 58,69</t>
+          <t>36,34; 58,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 50,28</t>
+          <t>29,92; 50,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,41; 58,44</t>
+          <t>44,12; 58,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,17; 36,03</t>
+          <t>15,22; 36,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 41,82</t>
+          <t>19,3; 42,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,89; 23,47</t>
+          <t>9,84; 24,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 29,47</t>
+          <t>13,17; 29,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,54; 32,46</t>
+          <t>14,48; 31,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,37; 53,3</t>
+          <t>32,35; 52,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 43,92</t>
+          <t>24,57; 43,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,99; 51,6</t>
+          <t>38,22; 50,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 30,34</t>
+          <t>16,95; 30,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,64; 44,91</t>
+          <t>29,91; 44,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 32,52</t>
+          <t>20,12; 33,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,13; 40,54</t>
+          <t>30,21; 40,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 33,05</t>
+          <t>11,15; 32,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,98; 39,93</t>
+          <t>14,93; 40,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 34,14</t>
+          <t>14,14; 34,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 45,08</t>
+          <t>28,7; 45,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,41; 54,52</t>
+          <t>31,9; 53,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 43,76</t>
+          <t>23,35; 44,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,72; 33,29</t>
+          <t>12,97; 33,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,93; 59,6</t>
+          <t>43,51; 59,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,13; 42,95</t>
+          <t>26,75; 42,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,01; 37,97</t>
+          <t>22,62; 39,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 30,65</t>
+          <t>15,63; 29,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,92; 50,38</t>
+          <t>38,92; 51,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 38,44</t>
+          <t>16,2; 39,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 45,77</t>
+          <t>22,35; 46,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,93; 34,16</t>
+          <t>14,14; 34,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 31,5</t>
+          <t>16,6; 32,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 54,98</t>
+          <t>31,91; 55,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,68; 57,83</t>
+          <t>36,3; 58,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,81; 43,88</t>
+          <t>22,06; 44,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 40,94</t>
+          <t>29,43; 42,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 45,34</t>
+          <t>29,12; 45,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,02; 49,64</t>
+          <t>33,39; 49,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 35,75</t>
+          <t>21,45; 36,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 34,89</t>
+          <t>25,55; 34,86</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 47,94</t>
+          <t>15,65; 46,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 44,94</t>
+          <t>13,04; 46,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 22,23</t>
+          <t>4,73; 22,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 37,07</t>
+          <t>16,69; 37,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 54,26</t>
+          <t>23,89; 52,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,24; 63,49</t>
+          <t>37,67; 64,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89; 63,75</t>
+          <t>33,49; 63,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,22; 36,86</t>
+          <t>22,88; 36,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,36; 44,45</t>
+          <t>24,16; 46,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,66; 52,61</t>
+          <t>31,74; 53,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,34; 42,42</t>
+          <t>22,94; 42,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,39; 34,34</t>
+          <t>22,48; 34,43</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,65; 52,85</t>
+          <t>25,65; 52,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,6; 49,11</t>
+          <t>22,59; 51,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,2; 44,26</t>
+          <t>20,42; 44,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,53; 48,73</t>
+          <t>32,07; 48,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,95; 51,82</t>
+          <t>28,44; 51,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,84; 42,42</t>
+          <t>19,92; 42,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,75; 47,3</t>
+          <t>22,82; 49,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,22; 57,65</t>
+          <t>44,06; 58,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,43; 49,2</t>
+          <t>30,4; 47,83</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,39; 40,73</t>
+          <t>24,37; 40,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,37; 41,95</t>
+          <t>24,15; 41,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,24; 51,48</t>
+          <t>40,34; 51,68</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,49; 27,21</t>
+          <t>11,19; 26,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,71; 35,25</t>
+          <t>17,77; 36,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,39; 33,11</t>
+          <t>16,92; 32,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,74; 24,9</t>
+          <t>13,18; 25,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,37; 43,43</t>
+          <t>25,24; 42,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,72; 43,2</t>
+          <t>27,36; 43,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,57; 50,89</t>
+          <t>32,7; 50,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 41,64</t>
+          <t>3,53; 41,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,84; 32,75</t>
+          <t>20,58; 32,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,13; 37,07</t>
+          <t>24,99; 37,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,85</t>
+          <t>28,86; 41,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 30,93</t>
+          <t>5,61; 30,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,62; 41,14</t>
+          <t>24,31; 40,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,7</t>
+          <t>11,01; 26,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,26; 25,8</t>
+          <t>12,54; 25,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 18,5</t>
+          <t>9,61; 19,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,29; 39,76</t>
+          <t>23,98; 39,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,88; 39,14</t>
+          <t>23,62; 38,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,43; 41,45</t>
+          <t>24,7; 40,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,18; 40,68</t>
+          <t>30,56; 40,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,47; 37,94</t>
+          <t>26,35; 37,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 30,47</t>
+          <t>19,84; 30,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,37; 31,84</t>
+          <t>21,14; 31,67</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,47; 29,54</t>
+          <t>22,26; 29,62</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,2</t>
+          <t>22,92; 30,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,08; 31,0</t>
+          <t>22,81; 30,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,94; 24,15</t>
+          <t>17,87; 24,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,65; 28,14</t>
+          <t>22,59; 28,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,03</t>
+          <t>31,02; 38,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,18; 42,4</t>
+          <t>35,09; 42,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,84; 39,11</t>
+          <t>32,28; 39,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,34; 42,22</t>
+          <t>17,41; 42,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,02; 33,51</t>
+          <t>28,22; 33,56</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,78; 36,16</t>
+          <t>30,76; 36,14</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27,09; 32,14</t>
+          <t>26,86; 32,05</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,06; 34,9</t>
+          <t>20,6; 35,06</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4443; 13948</t>
+          <t>4550; 15266</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8048; 20470</t>
+          <t>8190; 20847</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4895; 14334</t>
+          <t>4894; 15145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21400; 33554</t>
+          <t>21791; 33726</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5328; 16392</t>
+          <t>4791; 17587</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23382; 36637</t>
+          <t>23490; 36907</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18911; 33418</t>
+          <t>17993; 33360</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28046; 38766</t>
+          <t>27919; 39157</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12348; 27502</t>
+          <t>12318; 27275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34403; 54685</t>
+          <t>33856; 54197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24957; 44393</t>
+          <t>26417; 44893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52984; 69730</t>
+          <t>52642; 69633</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10108; 24014</t>
+          <t>10143; 24611</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15062; 33122</t>
+          <t>15283; 33503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7761; 20486</t>
+          <t>8590; 21101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10111; 23535</t>
+          <t>10513; 23629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15213; 31771</t>
+          <t>14175; 31043</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34067; 54417</t>
+          <t>33023; 53655</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27728; 50610</t>
+          <t>28316; 50383</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48805; 66288</t>
+          <t>49098; 65400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28156; 49910</t>
+          <t>27880; 50132</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53728; 81427</t>
+          <t>54217; 81377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39629; 65857</t>
+          <t>40753; 68247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62760; 84441</t>
+          <t>62937; 84952</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5669; 16835</t>
+          <t>5678; 16471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8349; 22258</t>
+          <t>8324; 22527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9064; 21695</t>
+          <t>8987; 21849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20122; 33126</t>
+          <t>21095; 33616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27068; 45534</t>
+          <t>26642; 44955</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18089; 34997</t>
+          <t>18671; 35560</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10163; 26595</t>
+          <t>10361; 26885</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38161; 51764</t>
+          <t>37790; 51868</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36482; 57750</t>
+          <t>35962; 56689</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29874; 51532</t>
+          <t>30702; 53426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22751; 43970</t>
+          <t>22420; 42349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62415; 80783</t>
+          <t>62407; 81921</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9183; 21189</t>
+          <t>8929; 21717</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14450; 29304</t>
+          <t>14312; 29472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9017; 22106</t>
+          <t>9152; 22245</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11970; 22973</t>
+          <t>12104; 23566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24409; 40857</t>
+          <t>23714; 41078</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31388; 49486</t>
+          <t>31064; 49690</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19969; 40180</t>
+          <t>20203; 40322</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30581; 42428</t>
+          <t>30503; 43546</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38064; 58687</t>
+          <t>37693; 58962</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49402; 74263</t>
+          <t>49955; 74033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32212; 55865</t>
+          <t>33529; 56979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45182; 61603</t>
+          <t>45105; 61552</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4957; 14068</t>
+          <t>4593; 13703</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4308; 14206</t>
+          <t>4123; 14547</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1652; 9353</t>
+          <t>1992; 9515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5884; 12907</t>
+          <t>5812; 13156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9963; 22380</t>
+          <t>9854; 21685</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18068; 31653</t>
+          <t>18779; 32382</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17127; 32215</t>
+          <t>16926; 32021</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13085; 21710</t>
+          <t>13478; 21243</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16494; 31378</t>
+          <t>17052; 32903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24976; 42863</t>
+          <t>25861; 43550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20686; 39290</t>
+          <t>21248; 39406</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20978; 32178</t>
+          <t>21069; 32260</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12106; 24945</t>
+          <t>12104; 24946</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11696; 25415</t>
+          <t>11694; 26554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9787; 21440</t>
+          <t>9895; 21385</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18999; 29366</t>
+          <t>19328; 28949</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19650; 36434</t>
+          <t>19999; 36240</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13932; 29781</t>
+          <t>13990; 29584</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14657; 31873</t>
+          <t>15381; 33275</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28508; 37164</t>
+          <t>28403; 37949</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35752; 57815</t>
+          <t>35717; 56206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29750; 49680</t>
+          <t>29725; 49754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28232; 48591</t>
+          <t>27976; 48498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50192; 64202</t>
+          <t>50308; 64462</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13227; 28819</t>
+          <t>11856; 27654</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19885; 39572</t>
+          <t>19954; 40409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19504; 37149</t>
+          <t>18983; 36579</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15615; 30512</t>
+          <t>16149; 31293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29711; 50865</t>
+          <t>29563; 49453</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37935; 61321</t>
+          <t>38841; 62250</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49559; 75130</t>
+          <t>48271; 74626</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15340; 140544</t>
+          <t>11914; 140778</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46481; 73050</t>
+          <t>45908; 71921</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63889; 94235</t>
+          <t>63540; 95327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73918; 106120</t>
+          <t>74993; 106663</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24376; 142316</t>
+          <t>25802; 142109</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26426; 46028</t>
+          <t>27202; 45578</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11988; 31035</t>
+          <t>13295; 31629</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17795; 34609</t>
+          <t>16821; 33959</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13710; 26750</t>
+          <t>13901; 27585</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37218; 60930</t>
+          <t>36736; 61048</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39259; 64346</t>
+          <t>38834; 62961</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43064; 73067</t>
+          <t>43552; 70930</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>56120; 75642</t>
+          <t>56828; 75704</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70182; 100586</t>
+          <t>69857; 100231</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57079; 86892</t>
+          <t>56567; 87303</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66361; 98852</t>
+          <t>65618; 98329</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>74287; 97653</t>
+          <t>73580; 97921</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>114697; 151761</t>
+          <t>115143; 152959</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>129139; 173471</t>
+          <t>127667; 172407</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106103; 142797</t>
+          <t>105641; 143942</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145980; 181314</t>
+          <t>145589; 180902</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>207894; 257407</t>
+          <t>209951; 260274</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>261377; 315014</t>
+          <t>260717; 316377</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>247689; 304264</t>
+          <t>251097; 306449</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>178478; 434506</t>
+          <t>179236; 433745</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>330432; 395194</t>
+          <t>332744; 395723</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>400951; 471055</t>
+          <t>400732; 470735</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>370897; 440086</t>
+          <t>367801; 438824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>352520; 584126</t>
+          <t>344724; 586783</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 43,14</t>
+          <t>12,71; 41,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 47,08</t>
+          <t>17,55; 45,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 38,94</t>
+          <t>11,88; 36,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,98; 60,33</t>
+          <t>38,42; 60,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 44,83</t>
+          <t>12,8; 42,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,04; 75,48</t>
+          <t>47,41; 75,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,43; 67,54</t>
+          <t>37,95; 68,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>44,03; 61,75</t>
+          <t>43,75; 60,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,51; 36,55</t>
+          <t>16,83; 36,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,34; 58,17</t>
+          <t>36,22; 57,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,92; 50,85</t>
+          <t>29,02; 49,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,12; 58,36</t>
+          <t>43,77; 57,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 36,92</t>
+          <t>14,78; 36,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,3; 42,3</t>
+          <t>18,39; 42,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 24,17</t>
+          <t>9,37; 24,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 29,59</t>
+          <t>12,54; 28,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 31,72</t>
+          <t>15,58; 32,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,35; 52,56</t>
+          <t>33,05; 53,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 43,73</t>
+          <t>24,49; 44,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,22; 50,91</t>
+          <t>38,73; 52,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 30,47</t>
+          <t>17,62; 30,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 44,89</t>
+          <t>29,89; 45,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 33,7</t>
+          <t>19,88; 32,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 40,78</t>
+          <t>30,04; 40,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 32,33</t>
+          <t>10,98; 31,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 40,41</t>
+          <t>15,08; 40,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,14; 34,38</t>
+          <t>14,88; 33,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 45,74</t>
+          <t>27,57; 45,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,9; 53,83</t>
+          <t>32,9; 53,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,35; 44,47</t>
+          <t>23,11; 44,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,97; 33,65</t>
+          <t>13,3; 33,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,51; 59,72</t>
+          <t>45,64; 61,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,75; 42,16</t>
+          <t>27,07; 42,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,62; 39,37</t>
+          <t>22,63; 38,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 29,52</t>
+          <t>15,77; 31,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,92; 51,09</t>
+          <t>39,4; 51,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 39,4</t>
+          <t>17,08; 39,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 46,03</t>
+          <t>22,21; 46,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 34,38</t>
+          <t>15,15; 34,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 32,31</t>
+          <t>15,65; 30,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,91; 55,28</t>
+          <t>32,54; 54,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,3; 58,07</t>
+          <t>36,84; 58,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,06; 44,03</t>
+          <t>21,89; 44,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,43; 42,02</t>
+          <t>28,89; 40,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,12; 45,55</t>
+          <t>29,57; 46,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,39; 49,49</t>
+          <t>32,49; 49,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,45; 36,46</t>
+          <t>21,31; 36,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,55; 34,86</t>
+          <t>25,15; 34,71</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,65; 46,69</t>
+          <t>17,26; 47,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,04; 46,02</t>
+          <t>13,81; 47,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 22,61</t>
+          <t>5,49; 22,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,69; 37,79</t>
+          <t>17,19; 37,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,89; 52,57</t>
+          <t>23,49; 54,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 64,95</t>
+          <t>35,9; 63,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,49; 63,37</t>
+          <t>32,78; 63,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,88; 36,07</t>
+          <t>23,2; 38,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 46,61</t>
+          <t>23,24; 46,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,74; 53,46</t>
+          <t>30,99; 53,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 42,55</t>
+          <t>21,5; 41,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,48; 34,43</t>
+          <t>21,89; 33,8</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,65; 52,86</t>
+          <t>23,35; 51,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,59; 51,31</t>
+          <t>22,76; 49,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 44,14</t>
+          <t>20,32; 42,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,07; 48,04</t>
+          <t>32,57; 48,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,44; 51,54</t>
+          <t>27,82; 51,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,92; 42,14</t>
+          <t>19,88; 41,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,82; 49,38</t>
+          <t>22,44; 48,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,06; 58,87</t>
+          <t>42,92; 58,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,4; 47,83</t>
+          <t>30,23; 47,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,37; 40,79</t>
+          <t>24,69; 41,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,15; 41,87</t>
+          <t>24,58; 42,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,34; 51,68</t>
+          <t>40,33; 51,42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,19; 26,11</t>
+          <t>12,43; 26,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,77; 36,0</t>
+          <t>18,59; 36,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,92; 32,61</t>
+          <t>17,71; 33,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,54</t>
+          <t>12,83; 25,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 42,22</t>
+          <t>25,16; 42,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,36; 43,85</t>
+          <t>26,28; 42,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,7; 50,55</t>
+          <t>32,93; 49,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 41,7</t>
+          <t>33,35; 45,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,58; 32,24</t>
+          <t>20,58; 32,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,99; 37,5</t>
+          <t>25,03; 37,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,86; 41,05</t>
+          <t>28,02; 40,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 30,89</t>
+          <t>25,11; 33,94</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,31; 40,73</t>
+          <t>23,32; 40,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,01; 26,19</t>
+          <t>10,82; 26,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,54; 25,31</t>
+          <t>12,84; 25,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,61; 19,07</t>
+          <t>9,8; 18,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,84</t>
+          <t>24,71; 39,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,62; 38,29</t>
+          <t>23,32; 38,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,7; 40,23</t>
+          <t>24,99; 40,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>30,56; 40,71</t>
+          <t>31,2; 41,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,35; 37,81</t>
+          <t>26,73; 38,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,84; 30,61</t>
+          <t>19,41; 30,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,14; 31,67</t>
+          <t>20,6; 31,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,62</t>
+          <t>23,01; 30,34</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22,92; 30,44</t>
+          <t>22,74; 30,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,81</t>
+          <t>22,85; 30,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,34</t>
+          <t>17,9; 24,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,59; 28,07</t>
+          <t>22,38; 27,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,45</t>
+          <t>30,92; 38,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,09; 42,58</t>
+          <t>34,82; 42,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,28; 39,39</t>
+          <t>31,89; 39,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,41; 42,14</t>
+          <t>38,85; 43,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,22; 33,56</t>
+          <t>28,38; 33,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,76; 36,14</t>
+          <t>30,78; 36,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26,86; 32,05</t>
+          <t>26,61; 31,63</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,6; 35,06</t>
+          <t>32,18; 35,88</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27759</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>33314</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61074</t>
+          <t>63927</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4550; 15266</t>
+          <t>4498; 14711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8190; 20847</t>
+          <t>7770; 20203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4894; 15145</t>
+          <t>4622; 14335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21791; 33726</t>
+          <t>23418; 36637</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4791; 17587</t>
+          <t>5023; 16670</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23490; 36907</t>
+          <t>23180; 36911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17993; 33360</t>
+          <t>18743; 33661</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27919; 39157</t>
+          <t>28556; 39618</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12318; 27275</t>
+          <t>12557; 27037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33856; 54197</t>
+          <t>33746; 53947</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26417; 44893</t>
+          <t>25624; 44044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52642; 69633</t>
+          <t>55251; 72444</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>60938</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73497</t>
+          <t>78330</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10143; 24611</t>
+          <t>9855; 24391</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15283; 33503</t>
+          <t>14569; 33789</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8590; 21101</t>
+          <t>8175; 21220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10513; 23629</t>
+          <t>10964; 24492</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14175; 31043</t>
+          <t>15249; 32239</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33023; 53655</t>
+          <t>33739; 54714</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28316; 50383</t>
+          <t>28217; 51544</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49098; 65400</t>
+          <t>52195; 70215</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27880; 50132</t>
+          <t>28991; 50782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54217; 81377</t>
+          <t>54181; 82643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40753; 68247</t>
+          <t>40255; 65691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62937; 84952</t>
+          <t>66747; 90720</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44891</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>71340</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5678; 16471</t>
+          <t>5593; 16137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8324; 22527</t>
+          <t>8406; 22352</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8987; 21849</t>
+          <t>9453; 21022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21095; 33616</t>
+          <t>19929; 32835</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26642; 44955</t>
+          <t>27475; 44858</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18671; 35560</t>
+          <t>18483; 35721</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10361; 26885</t>
+          <t>10628; 26554</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37790; 51868</t>
+          <t>38919; 52149</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35962; 56689</t>
+          <t>36401; 57168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30702; 53426</t>
+          <t>30714; 52717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22420; 42349</t>
+          <t>22624; 44618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62407; 81921</t>
+          <t>62087; 81130</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38519</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>56865</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8929; 21717</t>
+          <t>9414; 21922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14312; 29472</t>
+          <t>14218; 29479</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9152; 22245</t>
+          <t>9805; 22472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12104; 23566</t>
+          <t>12738; 24623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23714; 41078</t>
+          <t>24184; 40741</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31064; 49690</t>
+          <t>31522; 49889</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20203; 40322</t>
+          <t>20045; 40348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30503; 43546</t>
+          <t>31928; 45088</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37693; 58962</t>
+          <t>38274; 59583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49955; 74033</t>
+          <t>48612; 73669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33529; 56979</t>
+          <t>33311; 57266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45105; 61552</t>
+          <t>48261; 66616</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17268</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26260</t>
+          <t>27201</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4593; 13703</t>
+          <t>5065; 13941</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4123; 14547</t>
+          <t>4366; 15036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1992; 9515</t>
+          <t>2310; 9457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5812; 13156</t>
+          <t>6273; 13869</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9854; 21685</t>
+          <t>9689; 22301</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18779; 32382</t>
+          <t>17896; 31895</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16926; 32021</t>
+          <t>16567; 31993</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13478; 21243</t>
+          <t>14189; 23331</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17052; 32903</t>
+          <t>16405; 32948</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25861; 43550</t>
+          <t>25251; 43570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21248; 39406</t>
+          <t>19911; 38493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21069; 32260</t>
+          <t>21376; 33009</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>33793</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57166</t>
+          <t>57860</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12104; 24946</t>
+          <t>11018; 24072</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11694; 26554</t>
+          <t>11779; 25515</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9895; 21385</t>
+          <t>9843; 20596</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19328; 28949</t>
+          <t>19616; 29195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19999; 36240</t>
+          <t>19560; 36328</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13990; 29584</t>
+          <t>13955; 28969</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15381; 33275</t>
+          <t>15121; 32485</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28403; 37949</t>
+          <t>28533; 39142</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35717; 56206</t>
+          <t>35527; 56353</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29725; 49754</t>
+          <t>30111; 50050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27976; 48498</t>
+          <t>28473; 49518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50308; 64462</t>
+          <t>51095; 65152</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>27845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>64076</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75016</t>
+          <t>91921</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11856; 27654</t>
+          <t>13163; 27864</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19954; 40409</t>
+          <t>20867; 40567</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18983; 36579</t>
+          <t>19868; 37134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16149; 31293</t>
+          <t>19315; 37948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29563; 49453</t>
+          <t>29473; 50002</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38841; 62250</t>
+          <t>37314; 60728</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48271; 74626</t>
+          <t>48619; 73794</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11914; 140778</t>
+          <t>54328; 74226</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45908; 71921</t>
+          <t>45906; 73118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63540; 95327</t>
+          <t>63629; 95399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74993; 106663</t>
+          <t>72795; 105443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25802; 142109</t>
+          <t>78717; 106391</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>76484</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>85588</t>
+          <t>98774</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27202; 45578</t>
+          <t>26093; 44983</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13295; 31629</t>
+          <t>13069; 31778</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16821; 33959</t>
+          <t>17225; 34799</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13901; 27585</t>
+          <t>15768; 30367</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>36736; 61048</t>
+          <t>37855; 60232</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38834; 62961</t>
+          <t>38347; 63096</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43552; 70930</t>
+          <t>44051; 71045</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>56828; 75704</t>
+          <t>66104; 87631</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69857; 100231</t>
+          <t>70863; 101420</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56567; 87303</t>
+          <t>55357; 85964</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65618; 98329</t>
+          <t>63951; 98931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>73580; 97921</t>
+          <t>85774; 113088</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>115143; 152959</t>
+          <t>114256; 153418</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>127667; 172407</t>
+          <t>127896; 172620</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105641; 143942</t>
+          <t>105867; 143017</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145589; 180902</t>
+          <t>158954; 197033</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>209951; 260274</t>
+          <t>209277; 259970</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>260717; 316377</t>
+          <t>258686; 313752</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>251097; 306449</t>
+          <t>248112; 305455</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>179236; 433745</t>
+          <t>348962; 390260</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>332744; 395723</t>
+          <t>334693; 394645</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>400732; 470735</t>
+          <t>400904; 469767</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>367801; 438824</t>
+          <t>364334; 433164</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>344724; 586783</t>
+          <t>517575; 577032</t>
         </is>
       </c>
     </row>
